--- a/moduli_aziende/aifecs/moduli_compilati/MOD-910-H-Performance.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-910-H-Performance.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8f647aa8ab47443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd90312d4b3914178"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -368,21 +351,19 @@
       </x:c>
       <x:c r="D2" s="6"/>
       <x:c r="E2" s="6" t="str">
-        <x:v>Proposta: 100%</x:v>
+        <x:v>100%</x:v>
       </x:c>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6" t="str">
         <x:v>Da rilevare</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>Definire periodo e campione. Nessun rilascio proposto con requisiti mancanti.</x:v>
+        <x:v>Definire periodo e campione. Verificare tutti i requisiti prima del rilascio.</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
         <x:v>DID / SEG</x:v>
       </x:c>
-      <x:c r="J2" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J2" s="6"/>
     </x:row>
     <x:row r="3" ht="50" customHeight="1">
       <x:c r="A3" s="5"/>
@@ -394,7 +375,7 @@
       </x:c>
       <x:c r="D3" s="6"/>
       <x:c r="E3" s="6" t="str">
-        <x:v>Proposta: 100%</x:v>
+        <x:v>100%</x:v>
       </x:c>
       <x:c r="F3" s="6"/>
       <x:c r="G3" s="6" t="str">
@@ -406,11 +387,9 @@
       <x:c r="I3" s="6" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="J3" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="68" customHeight="1">
+      <x:c r="J3" s="6"/>
+    </x:row>
+    <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="5"/>
       <x:c r="B4" s="6" t="str">
         <x:v>Rete</x:v>
@@ -420,7 +399,7 @@
       </x:c>
       <x:c r="D4" s="6"/>
       <x:c r="E4" s="6" t="str">
-        <x:v>Proposta: 100% del piano approvato</x:v>
+        <x:v>100% del piano approvato</x:v>
       </x:c>
       <x:c r="F4" s="6"/>
       <x:c r="G4" s="6" t="str">
@@ -432,9 +411,7 @@
       <x:c r="I4" s="6" t="str">
         <x:v>SOC / QUAL</x:v>
       </x:c>
-      <x:c r="J4" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J4" s="6"/>
     </x:row>
     <x:row r="5" ht="50" customHeight="1">
       <x:c r="A5" s="5"/>
@@ -446,7 +423,7 @@
       </x:c>
       <x:c r="D5" s="6"/>
       <x:c r="E5" s="6" t="str">
-        <x:v>Proposta: almeno 4/5</x:v>
+        <x:v>almeno 4/5</x:v>
       </x:c>
       <x:c r="F5" s="6"/>
       <x:c r="G5" s="6" t="str">
@@ -458,9 +435,7 @@
       <x:c r="I5" s="6" t="str">
         <x:v>QUAL / SEG</x:v>
       </x:c>
-      <x:c r="J5" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J5" s="6"/>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
       <x:c r="A6" s="5"/>
@@ -484,9 +459,7 @@
       <x:c r="I6" s="6" t="str">
         <x:v>QUAL / SEG</x:v>
       </x:c>
-      <x:c r="J6" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J6" s="6"/>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="5"/>
@@ -510,9 +483,7 @@
       <x:c r="I7" s="6" t="str">
         <x:v>SOC</x:v>
       </x:c>
-      <x:c r="J7" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J7" s="6"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="5"/>
@@ -536,9 +507,7 @@
       <x:c r="I8" s="6" t="str">
         <x:v>SEG</x:v>
       </x:c>
-      <x:c r="J8" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J8" s="6"/>
     </x:row>
     <x:row r="9" ht="50" customHeight="1">
       <x:c r="A9" s="5"/>
@@ -562,9 +531,7 @@
       <x:c r="I9" s="6" t="str">
         <x:v>SEG / QUAL</x:v>
       </x:c>
-      <x:c r="J9" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J9" s="6"/>
     </x:row>
     <x:row r="10" ht="50" customHeight="1">
       <x:c r="A10" s="5"/>
@@ -588,9 +555,7 @@
       <x:c r="I10" s="6" t="str">
         <x:v>QUAL / SOC</x:v>
       </x:c>
-      <x:c r="J10" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J10" s="6"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="5"/>
@@ -614,11 +579,9 @@
       <x:c r="I11" s="6" t="str">
         <x:v>IT</x:v>
       </x:c>
-      <x:c r="J11" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="68" customHeight="1">
+      <x:c r="J11" s="6"/>
+    </x:row>
+    <x:row r="12" ht="50" customHeight="1">
       <x:c r="A12" s="5"/>
       <x:c r="B12" s="6" t="str">
         <x:v>Competenze interne</x:v>
@@ -628,7 +591,7 @@
       </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6" t="str">
-        <x:v>Proposta: 100% del piano approvato</x:v>
+        <x:v>100% del piano approvato</x:v>
       </x:c>
       <x:c r="F12" s="6"/>
       <x:c r="G12" s="6" t="str">
@@ -640,9 +603,7 @@
       <x:c r="I12" s="6" t="str">
         <x:v>DID / QUAL</x:v>
       </x:c>
-      <x:c r="J12" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J12" s="6"/>
     </x:row>
     <x:row r="13" ht="50" customHeight="1">
       <x:c r="A13" s="5"/>
@@ -666,9 +627,7 @@
       <x:c r="I13" s="6" t="str">
         <x:v>QUAL</x:v>
       </x:c>
-      <x:c r="J13" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="J13" s="6"/>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="2"/>
@@ -888,6 +847,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa311dc911b6450b"/>
 </x:worksheet>
 </file>